--- a/artfynd/A 26552-2022 artfynd.xlsx
+++ b/artfynd/A 26552-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>132528620</v>
       </c>
       <c r="B2" t="n">
-        <v>56830</v>
+        <v>56831</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -797,7 +797,7 @@
         <v>132528624</v>
       </c>
       <c r="B3" t="n">
-        <v>56811</v>
+        <v>56812</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -916,7 +916,7 @@
         <v>132527476</v>
       </c>
       <c r="B4" t="n">
-        <v>56818</v>
+        <v>56819</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1025,7 +1025,7 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Johan Allmér, Maryam Bessouda</t>
+          <t>Maryam Bessouda, Johan Allmér</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>

--- a/artfynd/A 26552-2022 artfynd.xlsx
+++ b/artfynd/A 26552-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>132528620</v>
       </c>
       <c r="B2" t="n">
-        <v>56831</v>
+        <v>56835</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -797,7 +797,7 @@
         <v>132528624</v>
       </c>
       <c r="B3" t="n">
-        <v>56812</v>
+        <v>56816</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -916,7 +916,7 @@
         <v>132527476</v>
       </c>
       <c r="B4" t="n">
-        <v>56819</v>
+        <v>56823</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1025,7 +1025,7 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Maryam Bessouda, Johan Allmér</t>
+          <t>Johan Allmér, Maryam Bessouda</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>

--- a/artfynd/A 26552-2022 artfynd.xlsx
+++ b/artfynd/A 26552-2022 artfynd.xlsx
@@ -1025,7 +1025,7 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Johan Allmér, Maryam Bessouda</t>
+          <t>Maryam Bessouda, Johan Allmér</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>

--- a/artfynd/A 26552-2022 artfynd.xlsx
+++ b/artfynd/A 26552-2022 artfynd.xlsx
@@ -1025,7 +1025,7 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Maryam Bessouda, Johan Allmér</t>
+          <t>Johan Allmér, Maryam Bessouda</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>

--- a/artfynd/A 26552-2022 artfynd.xlsx
+++ b/artfynd/A 26552-2022 artfynd.xlsx
@@ -1021,7 +1021,7 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Maryam Bessouda, Johan Allmér</t>
+          <t>Johan Allmér, Maryam Bessouda</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>

--- a/artfynd/A 26552-2022 artfynd.xlsx
+++ b/artfynd/A 26552-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AY7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>132528620</v>
+        <v>99303487</v>
       </c>
       <c r="B2" t="n">
-        <v>56837</v>
+        <v>58435</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,54 +686,41 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>205995</v>
+        <v>100058</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Dvärgpipistrell</t>
+          <t>Mindre flugsnappare</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Pipistrellus pygmaeus</t>
+          <t>Ficedula parva</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(W.E.Leach, 1825)</t>
+          <t>(Bechstein, 1794)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>registreringar</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr"/>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>autobox med höghastighetsinspelning</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Forsmark, Upl</t>
+          <t>FM-108-1-20, Upl</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>673671</v>
+        <v>673728</v>
       </c>
       <c r="R2" t="n">
-        <v>6700744</v>
+        <v>6700775</v>
       </c>
       <c r="S2" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -757,17 +744,22 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2024-07-24</t>
+          <t>2013-05-22</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>05:42</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2024-07-26</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Fladdermusinventering</t>
+          <t>2013-05-22</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>05:42</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,22 +774,26 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Stina Hällholm</t>
+          <t>Mathias Andersson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Johan Allmér, Maryam Bessouda</t>
-        </is>
-      </c>
-      <c r="AY2" t="inlineStr"/>
+          <t>Via Mathias Andersson</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr">
+        <is>
+          <t>Forsmark platsundersökning</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>132528624</v>
+        <v>99303482</v>
       </c>
       <c r="B3" t="n">
-        <v>56816</v>
+        <v>58541</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -805,50 +801,41 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>205998</v>
+        <v>102987</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Nordfladdermus</t>
+          <t>Sädesärla</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Cnephaeus nilssonii</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr"/>
+          <t>Motacilla alba</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>80</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>registreringar</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr"/>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>autobox med höghastighetsinspelning</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Forsmark, Upl</t>
+          <t>FM-108-1-20, Upl</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>673671</v>
+        <v>673728</v>
       </c>
       <c r="R3" t="n">
-        <v>6700744</v>
+        <v>6700775</v>
       </c>
       <c r="S3" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -872,17 +859,22 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2024-07-24</t>
+          <t>2013-05-22</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>06:12</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2024-07-26</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Fladdermusinventering</t>
+          <t>2013-05-22</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>06:12</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -897,44 +889,48 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Stina Hällholm</t>
+          <t>Mathias Andersson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Johan Allmér, Maryam Bessouda</t>
-        </is>
-      </c>
-      <c r="AY3" t="inlineStr"/>
+          <t>Via Mathias Andersson</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr">
+        <is>
+          <t>Forsmark platsundersökning</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>132527476</v>
+        <v>99308790</v>
       </c>
       <c r="B4" t="n">
-        <v>56825</v>
+        <v>58238</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>205992</v>
+        <v>103012</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vattenfladdermus</t>
+          <t>Grönsångare</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Myotis daubentonii</t>
+          <t>Phylloscopus sibilatrix</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Kuhl, 1817)</t>
+          <t>(Bechstein, 1793)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -942,32 +938,19 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>registreringar</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr"/>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>autobox med höghastighetsinspelning</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Forsmark, Upl</t>
+          <t>FM-118-4-31, Upl</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>673671</v>
+        <v>673744</v>
       </c>
       <c r="R4" t="n">
-        <v>6700744</v>
+        <v>6700627</v>
       </c>
       <c r="S4" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -991,17 +974,22 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2024-06-26</t>
+          <t>2018-05-20</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>00:00</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2024-06-28</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Fladdermusinventering</t>
+          <t>2018-05-20</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>00:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1016,15 +1004,372 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
+          <t>Mathias Andersson</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Via Mathias Andersson</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr">
+        <is>
+          <t>Forsmark platsundersökning</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>132527476</v>
+      </c>
+      <c r="B5" t="n">
+        <v>56842</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>205992</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Vattenfladdermus</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Myotis daubentonii</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Kuhl, 1817)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>registreringar</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr"/>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>autobox med höghastighetsinspelning</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Forsmark, Upl</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>673671</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6700744</v>
+      </c>
+      <c r="S5" t="n">
+        <v>50</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Forsmark</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2024-06-26</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2024-06-28</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Fladdermusinventering</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
           <t>Stina Hällholm</t>
         </is>
       </c>
-      <c r="AX4" t="inlineStr">
+      <c r="AX5" t="inlineStr">
         <is>
           <t>Johan Allmér, Maryam Bessouda</t>
         </is>
       </c>
-      <c r="AY4" t="inlineStr"/>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>132527472</v>
+      </c>
+      <c r="B6" t="n">
+        <v>56854</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>205995</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Dvärgpipistrell</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Pipistrellus pygmaeus</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(W.E.Leach, 1825)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>registreringar</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr"/>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>autobox med höghastighetsinspelning</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Forsmark, Upl</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>673671</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6700744</v>
+      </c>
+      <c r="S6" t="n">
+        <v>50</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Forsmark</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2024-06-26</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2024-06-28</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Fladdermusinventering</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Stina Hällholm</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Johan Allmér, Maryam Bessouda</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>132528624</v>
+      </c>
+      <c r="B7" t="n">
+        <v>56833</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>205998</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Nordfladdermus</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Cnephaeus nilssonii</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr"/>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>registreringar</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr"/>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>autobox med höghastighetsinspelning</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Forsmark, Upl</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>673671</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6700744</v>
+      </c>
+      <c r="S7" t="n">
+        <v>50</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Forsmark</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2024-07-24</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2024-07-26</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Fladdermusinventering</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Stina Hällholm</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Johan Allmér, Maryam Bessouda</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 26552-2022 artfynd.xlsx
+++ b/artfynd/A 26552-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY7"/>
+  <dimension ref="A1:AZ7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -787,6 +792,11 @@
           <t>Forsmark platsundersökning</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/99303487</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -902,6 +912,11 @@
           <t>Forsmark platsundersökning</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/99303482</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1017,6 +1032,11 @@
           <t>Forsmark platsundersökning</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/99308790</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1136,6 +1156,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132527476</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1255,6 +1280,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132527472</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1370,8 +1400,21 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132528624</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>